--- a/docs/Final_Project_UI_Test_Cases.xlsx
+++ b/docs/Final_Project_UI_Test_Cases.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="1262">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -3379,6 +3379,369 @@
     <t xml:space="preserve">BUG-023; avtomatik</t>
   </si>
   <si>
+    <t xml:space="preserve">UI-HOM-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana səhifə yüklənir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Başlıq "Bank of Baku" ehtiva edir, məzmun boş deyil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avtomatik: home.spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-HOM-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Əsas menyu bölmələrinə linklər mövcuddur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az açın
+2. Menyu linklərini yoxlayın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kartlar, Kreditlər, Əmanətlər, Pul köçürmələri, Onlayn xidmətlər, Digər xidmətlər, Bank haqqında, Biznes linkləri var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-HOM-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner slayderi mövcuddur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ən azı 1 slayd göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-HOM-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer-də sosial şəbəkə linkləri var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az açın
+2. Footer linklərinə baxın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook, X, LinkedIn, Telegram, WhatsApp, YouTube linkləri var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-HOM-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer-də daxili səhifə linkləri var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank haqqında, Xəbərlər, Təklif və iradlar, Tez-tez verilən suallar linkləri var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-HOM-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana səhifədə son xəbərlər göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ən azı 3 xəbər linki göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-TRF-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pul köçürmələri bölməsi iki xidməti göstərir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Union və UPT TÖS göstərilir, başlıq düzgündür</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avtomatik: transfers.spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-TRF-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Union səhifəsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL və başlıq düzgündür, məzmun boş deyil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-TRF-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPT TÖS səhifəsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/pul-kocurmeleri/upt-tos açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-TRF-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menyuda köçürmə xidmətlərinin linkləri var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az açın
+2. Menyu linklərinə baxın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Union və UPT TÖS linkləri mövcuddur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-NWS-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəbərlər siyahısı yüklənir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ən azı 5 xəbər kartı göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avtomatik: news.spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-NWS-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hər xəbərin tarixi gg.aa.yyyy formatındadır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/xeberler açın
+2. Tarixlərə baxın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bütün tarixlər gg.aa.yyyy formatındadır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-NWS-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəbərlər yenidən köhnəyə sıralanıb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/xeberler açın
+2. Tarixləri müqayisə edin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarixlər azalan sıradadır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-NWS-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəbərin ətraflı səhifəsi açılır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/xeberler açın
+2. İlk xəbərə klik edin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəbər səhifəsi açılır, tarix və "Siyahıya geri dön" görünür</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-NWS-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Səhifələmə ikinci səhifəyə keçir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/xeberler açın
+2. 2 nömrəli səhifəyə klik edin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siyahı dəyişir, aktiv səhifə 2 olur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-NWS-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəbər şəkilləri yüklənir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sınıq şəkil yoxdur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onlayn xidmətlər bölməsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/onlayn-xidmetler açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Başlıq düzgündür, məzmun boş deyil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avtomatik: services.spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dostbank mobil bankçılıq səhifəsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Başlıq "Dostbank" ehtiva edir, məzmun kifayət qədərdir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digər xidmətlər bölməsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/diger-xidmetler açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Başlıq düzgündür</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariflər səhifəsində iki PDF linki var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tariflər səhifəsini açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiziki və hüquqi şəxs üzrə tarif PDF linkləri var, yeni tabda açılır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ səhifəsində suallar siyahısı var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. FAQ səhifəsini açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ən azı 5 sual, başlanğıcda hamısı bağlıdır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ sualına klik cavabı açır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. FAQ səhifəsini açın
+2. İlk suala klik edin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cavab görünür, aria-expanded=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ sualına ikinci klik cavabı bağlayır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. FAQ səhifəsini açın
+2. İlk suala iki dəfə klik edin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cavab bağlanır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Pay səhifəsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/diger-xidmetler/odenis-sistemleri/applepay açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL düzgündür, "Apple Pay" mətni var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Pay səhifəsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/diger-xidmetler/odenis-sistemleri/googlepay açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL düzgündür, "Google Pay" mətni var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loyallıq klubu səhifəsində üç bölmə var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Loyallıq klubu səhifəsini açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İmtiyazlar, kart növləri, üzvlük bölmələri var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tez-tez verilən suallar səhifəsi alt bölməyə yönləndirir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/top10 ünvanına yönləndirir, ən azı 3 sual var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-SRV-030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Təklif və iradlar səhifəsində əlaqə məlumatları göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/teklif-ve-iradlar açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Başlıq düzgündür, e-poçt və 145 nömrəsi göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-ABT-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank haqqında səhifəsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avtomatik: about.spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-CMP-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kampaniyalar səhifəsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Başlıq və "Kampaniyalar" bölməsi var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-CMP-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kredit kampaniyaları səhifəsində üç kampaniya var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/kreditler/kampaniyalar açın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maaşa özəl kredit, Kreditini bizə gətir, KOMİSSİYASIZ kredit göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-BIZ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biznes bölməsi açılır (avtomatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL düzgündür, məzmun boş deyil</t>
+  </si>
+  <si>
     <t xml:space="preserve">Üsul</t>
   </si>
   <si>
@@ -3395,6 +3758,21 @@
   </si>
   <si>
     <t xml:space="preserve">Seçim səbəbi: təkrarlanan, sabit lokatorlu və riskli sahə (məlum bug-ı nümayiş etdirir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke/oxuma yoxlaması, forma göndərilmir; home.spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke/oxuma yoxlaması, forma göndərilmir; transfers.spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke/oxuma yoxlaması, forma göndərilmir; news.spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke/oxuma yoxlaması, forma göndərilmir; services.spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke/oxuma yoxlaması, forma göndərilmir; about.spec</t>
   </si>
   <si>
     <t xml:space="preserve">Cəmi</t>
@@ -3920,7 +4298,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L243"/>
+  <dimension ref="A1:L275"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -12499,22 +12877,1174 @@
         <v>1102</v>
       </c>
     </row>
+    <row r="244" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F244" s="3"/>
+      <c r="G244" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J244" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K244" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L244" s="3" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F245" s="3"/>
+      <c r="G245" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H245" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J245" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K245" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L245" s="3" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F246" s="3"/>
+      <c r="G246" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H246" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J246" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K246" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L246" s="3" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F247" s="3"/>
+      <c r="G247" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H247" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J247" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K247" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L247" s="3" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F248" s="3"/>
+      <c r="G248" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H248" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J248" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K248" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L248" s="3" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F249" s="3"/>
+      <c r="G249" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H249" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J249" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K249" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L249" s="3" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="F250" s="3"/>
+      <c r="G250" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H250" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I250" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J250" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K250" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L250" s="3" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F251" s="3"/>
+      <c r="G251" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H251" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J251" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K251" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L251" s="3" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F252" s="3"/>
+      <c r="G252" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H252" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I252" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J252" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K252" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L252" s="3" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F253" s="3"/>
+      <c r="G253" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H253" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I253" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J253" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K253" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L253" s="3" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="F254" s="3"/>
+      <c r="G254" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H254" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I254" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J254" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K254" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L254" s="3" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F255" s="3"/>
+      <c r="G255" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J255" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K255" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L255" s="3" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F256" s="3"/>
+      <c r="G256" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H256" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J256" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K256" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L256" s="3" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F257" s="3"/>
+      <c r="G257" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H257" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J257" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K257" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L257" s="3" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F258" s="3"/>
+      <c r="G258" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H258" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J258" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K258" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L258" s="3" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="F259" s="3"/>
+      <c r="G259" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H259" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J259" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K259" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L259" s="3" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F260" s="3"/>
+      <c r="G260" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H260" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I260" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J260" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K260" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L260" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="F261" s="3"/>
+      <c r="G261" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H261" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J261" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K261" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L261" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F262" s="3"/>
+      <c r="G262" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H262" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I262" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J262" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K262" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L262" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F263" s="3"/>
+      <c r="G263" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H263" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I263" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J263" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K263" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L263" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F264" s="3"/>
+      <c r="G264" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H264" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I264" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J264" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K264" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L264" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F265" s="3"/>
+      <c r="G265" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H265" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I265" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J265" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K265" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L265" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F266" s="3"/>
+      <c r="G266" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H266" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I266" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J266" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K266" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L266" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F267" s="3"/>
+      <c r="G267" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H267" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I267" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J267" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K267" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L267" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F268" s="3"/>
+      <c r="G268" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H268" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I268" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J268" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K268" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L268" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F269" s="3"/>
+      <c r="G269" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H269" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I269" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J269" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K269" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L269" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="F270" s="3"/>
+      <c r="G270" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H270" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I270" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J270" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K270" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L270" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F271" s="3"/>
+      <c r="G271" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H271" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I271" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J271" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K271" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L271" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="F272" s="3"/>
+      <c r="G272" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H272" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I272" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J272" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K272" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L272" s="3" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F273" s="3"/>
+      <c r="G273" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H273" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I273" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J273" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K273" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L273" s="3" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F274" s="3"/>
+      <c r="G274" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H274" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I274" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J274" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K274" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L274" s="3" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="F275" s="3"/>
+      <c r="G275" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H275" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J275" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K275" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L275" s="3" t="s">
+        <v>1210</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L243"/>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H257" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H400" type="list">
       <formula1>"Yüksək,Orta,Aşağı"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I257" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I400" type="list">
       <formula1>"Pozitiv,Neqativ,Sərhəd"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J257" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J400" type="list">
       <formula1>"Bəli,Yox"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K257" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K400" type="list">
       <formula1>"İcra olunmayıb,Keçdi,Uğursuz,Bloklanıb"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12535,7 +14065,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -12560,7 +14090,7 @@
         <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1103</v>
+        <v>1221</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>11</v>
@@ -12580,10 +14110,10 @@
         <v>18</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12600,10 +14130,10 @@
         <v>18</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12620,10 +14150,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12640,10 +14170,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12660,10 +14190,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12680,10 +14210,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1106</v>
+        <v>1224</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12700,10 +14230,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12720,10 +14250,10 @@
         <v>34</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12740,10 +14270,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12760,10 +14290,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12780,10 +14310,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12800,10 +14330,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12820,10 +14350,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12840,10 +14370,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12860,10 +14390,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12880,10 +14410,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12900,10 +14430,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12920,10 +14450,10 @@
         <v>34</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12940,10 +14470,10 @@
         <v>34</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12960,10 +14490,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12980,10 +14510,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13000,10 +14530,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13020,10 +14550,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1106</v>
+        <v>1224</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13040,10 +14570,10 @@
         <v>34</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1106</v>
+        <v>1224</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13060,10 +14590,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13080,10 +14610,10 @@
         <v>34</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>1105</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13100,10 +14630,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13120,10 +14650,10 @@
         <v>34</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13140,10 +14670,10 @@
         <v>34</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13160,10 +14690,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13180,10 +14710,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13200,10 +14730,10 @@
         <v>34</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13220,10 +14750,10 @@
         <v>34</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13240,10 +14770,10 @@
         <v>34</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13260,10 +14790,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13280,10 +14810,10 @@
         <v>76</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13300,10 +14830,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13320,10 +14850,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13340,10 +14870,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13360,10 +14890,10 @@
         <v>34</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13380,10 +14910,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>1108</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13400,10 +14930,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>1108</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13420,10 +14950,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1108</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13440,10 +14970,10 @@
         <v>76</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>1108</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13460,10 +14990,10 @@
         <v>76</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>1108</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13480,10 +15010,10 @@
         <v>76</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>1108</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13500,10 +15030,10 @@
         <v>34</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13520,10 +15050,10 @@
         <v>34</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13540,10 +15070,10 @@
         <v>34</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13560,10 +15090,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13580,10 +15110,10 @@
         <v>34</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13600,10 +15130,10 @@
         <v>34</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13620,10 +15150,10 @@
         <v>34</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>1107</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13640,10 +15170,10 @@
         <v>34</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>1104</v>
+        <v>1222</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>1108</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13660,10 +15190,650 @@
         <v>76</v>
       </c>
       <c r="E56" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>1104</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="D57" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>1108</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>1231</v>
       </c>
     </row>
   </sheetData>
@@ -13696,16 +15866,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1109</v>
+        <v>1232</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1110</v>
+        <v>1233</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>175</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13756,11 +15926,11 @@
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">COUNTIF('Test Case-lər'!B:B,A4)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A4,'Test Case-lər'!J:J,"Bəli")</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A4,'Test Case-lər'!K:K,"Uğursuz")</f>
@@ -13768,7 +15938,7 @@
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A4,'Test Case-lər'!H:H,"Yüksək")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13861,11 +16031,11 @@
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">COUNTIF('Test Case-lər'!B:B,A9)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A9,'Test Case-lər'!J:J,"Bəli")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A9,'Test Case-lər'!K:K,"Uğursuz")</f>
@@ -13882,11 +16052,11 @@
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">COUNTIF('Test Case-lər'!B:B,A10)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A10,'Test Case-lər'!J:J,"Bəli")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A10,'Test Case-lər'!K:K,"Uğursuz")</f>
@@ -13903,11 +16073,11 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">COUNTIF('Test Case-lər'!B:B,A11)</f>
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A11,'Test Case-lər'!J:J,"Bəli")</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A11,'Test Case-lər'!K:K,"Uğursuz")</f>
@@ -13924,11 +16094,11 @@
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">COUNTIF('Test Case-lər'!B:B,A12)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A12,'Test Case-lər'!J:J,"Bəli")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A12,'Test Case-lər'!K:K,"Uğursuz")</f>
@@ -13945,11 +16115,11 @@
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">COUNTIF('Test Case-lər'!B:B,A13)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A13,'Test Case-lər'!J:J,"Bəli")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A13,'Test Case-lər'!K:K,"Uğursuz")</f>
@@ -13966,11 +16136,11 @@
       </c>
       <c r="B14" s="5" t="n">
         <f aca="false">COUNTIF('Test Case-lər'!B:B,A14)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A14,'Test Case-lər'!J:J,"Bəli")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A14,'Test Case-lər'!K:K,"Uğursuz")</f>
@@ -14050,11 +16220,11 @@
       </c>
       <c r="B18" s="5" t="n">
         <f aca="false">COUNTIF('Test Case-lər'!B:B,A18)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C18" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A18,'Test Case-lər'!J:J,"Bəli")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D18" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A18,'Test Case-lər'!K:K,"Uğursuz")</f>
@@ -14062,7 +16232,7 @@
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">COUNTIFS('Test Case-lər'!B:B,A18,'Test Case-lər'!H:H,"Yüksək")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14214,15 +16384,15 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1109</v>
+        <v>1232</v>
       </c>
       <c r="B26" s="6" t="n">
         <f aca="false">SUM(B2:B25)</f>
-        <v>242</v>
+        <v>274</v>
       </c>
       <c r="C26" s="6" t="n">
         <f aca="false">SUM(C2:C25)</f>
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="D26" s="6" t="n">
         <f aca="false">SUM(D2:D25)</f>
@@ -14230,7 +16400,7 @@
       </c>
       <c r="E26" s="6" t="n">
         <f aca="false">SUM(E2:E25)</f>
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -14261,19 +16431,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>1112</v>
+        <v>1235</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1113</v>
+        <v>1236</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1114</v>
+        <v>1237</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1115</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14281,16 +16451,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1116</v>
+        <v>1239</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1117</v>
+        <v>1240</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1118</v>
+        <v>1241</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1119</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14298,16 +16468,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1116</v>
+        <v>1239</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1120</v>
+        <v>1243</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1121</v>
+        <v>1244</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1122</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14315,16 +16485,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1116</v>
+        <v>1239</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1123</v>
+        <v>1246</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1124</v>
+        <v>1247</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1125</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14332,16 +16502,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1126</v>
+        <v>1249</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1127</v>
+        <v>1250</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1128</v>
+        <v>1251</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1129</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14349,16 +16519,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1130</v>
+        <v>1253</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1131</v>
+        <v>1254</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1132</v>
+        <v>1255</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1133</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14366,16 +16536,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1130</v>
+        <v>1253</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1134</v>
+        <v>1257</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1135</v>
+        <v>1258</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1136</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14386,13 +16556,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1137</v>
+        <v>1260</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1138</v>
+        <v>1261</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Final_Project_UI_Test_Cases.xlsx
+++ b/docs/Final_Project_UI_Test_Cases.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3581" uniqueCount="1312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3601" uniqueCount="1326">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Uğursuz</t>
   </si>
   <si>
-    <t xml:space="preserve">/en məzmunu İngilis dilindədir, lakin html lang="az" və başlıq Azərbaycan dilində qalır (OBS-016)</t>
+    <t xml:space="preserve">/en məzmunu İngilis dilindədir, lakin html lang="az" və başlıq Azərbaycan dilində qalır (BUG-032)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-LNG-004</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Məzmun Rus dilindədir; html lang="ru"</t>
   </si>
   <si>
-    <t xml:space="preserve">/ru məzmunu Rus dilindədir, lakin html lang="az" və başlıq Azərbaycan dilində qalır (OBS-016)</t>
+    <t xml:space="preserve">/ru məzmunu Rus dilindədir, lakin html lang="az" və başlıq Azərbaycan dilində qalır (BUG-032)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-LNG-005</t>
@@ -1435,7 +1435,7 @@
     <t xml:space="preserve">Bitmiş kampaniya aktiv kimi görünmür</t>
   </si>
   <si>
-    <t xml:space="preserve">Vaxtı bitmiş müsabiqə (17–27 iyul 2026) hələ də siyahıdadır (OBS-015)</t>
+    <t xml:space="preserve">Vaxtı bitmiş müsabiqə (17–27 iyul 2026) hələ də siyahıdadır (BUG-031)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-CMP-003</t>
@@ -1480,7 +1480,7 @@
     <t xml:space="preserve">Məlumat və keçidlər düzgündür</t>
   </si>
   <si>
-    <t xml:space="preserve">/az/biznes: biznes kreditləri bannerləri və Müraciət et düymələri var; başlıq ana səhifə başlığıdır (OBS-016-a baxın)</t>
+    <t xml:space="preserve">/az/biznes: biznes kreditləri bannerləri və Müraciət et düymələri var; başlıq ana səhifə başlığıdır (BUG-032-a baxın)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-ABT-001</t>
@@ -1510,7 +1510,7 @@
     <t xml:space="preserve">Məzmun və yükləmə linkləri işləyir</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-011: bəzi ünvanlar yönləndirilir</t>
+    <t xml:space="preserve">BUG-030: bəzi ünvanlar yönləndirilir</t>
   </si>
   <si>
     <t xml:space="preserve">UI-ABT-003</t>
@@ -1543,7 +1543,7 @@
     <t xml:space="preserve">Xəritə/siyahı görünür</t>
   </si>
   <si>
-    <t xml:space="preserve">Real Chrome-da xəritə yüklənir (daxili brauzerdə OBS-003 artefaktı idi)</t>
+    <t xml:space="preserve">Real Chrome-da xəritə yüklənir (daxili brauzerdə artefakt idi)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-BRN-002</t>
@@ -1681,7 +1681,7 @@
     <t xml:space="preserve">Spred məntiqli həddədir</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-001: GBP 2.0000/2.2800, RUB 1.2000/2.0100</t>
+    <t xml:space="preserve">Müşahidə: GBP 2.0000/2.2800, RUB 1.2000/2.0100</t>
   </si>
   <si>
     <t xml:space="preserve">UI-FX-004</t>
@@ -2008,7 +2008,7 @@
     <t xml:space="preserve">HSTS, X-Content-Type-Options, X-Frame-Options/CSP mövcuddur</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-010: CSP məhduddur</t>
+    <t xml:space="preserve">Müşahidə: CSP məhduddur</t>
   </si>
   <si>
     <t xml:space="preserve">UI-SEC-003</t>
@@ -2038,7 +2038,7 @@
     <t xml:space="preserve">Mətn kimi göstərilir</t>
   </si>
   <si>
-    <t xml:space="preserve">WAF "&lt;" simvolunu bloklayır (OBS-004)</t>
+    <t xml:space="preserve">WAF "&lt;" simvolunu bloklayır (BUG-027)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-SEC-005</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">Məcburi olmayan kukilər üçün imtina variantı var</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-009: banner yoxdur, izləmə kukiləri qurulur</t>
+    <t xml:space="preserve">Müşahidə: banner yoxdur, izləmə kukiləri qurulur</t>
   </si>
   <si>
     <t xml:space="preserve">UI-EXT-001</t>
@@ -2304,7 +2304,7 @@
     <t xml:space="preserve">Mövcuddur, düzgündür</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-011: sitemap-da yönləndirilən ünvanlar</t>
+    <t xml:space="preserve">BUG-030: sitemap-da yönləndirilən ünvanlar</t>
   </si>
   <si>
     <t xml:space="preserve">UI-CHT-001</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">169.00 (Alış 1.6900)</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-002: 170.00 göstərilir</t>
+    <t xml:space="preserve">Müşahidə: 170.00 göstərilir</t>
   </si>
   <si>
     <t xml:space="preserve">UI-SRC-006</t>
@@ -2487,7 +2487,7 @@
     <t xml:space="preserve">"Nəticə tapılmadı" mesajı</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-005: yalnız "0 Nəticə"</t>
+    <t xml:space="preserve">BUG-028: yalnız "0 Nəticə"</t>
   </si>
   <si>
     <t xml:space="preserve">UI-SRC-009</t>
@@ -2505,7 +2505,7 @@
     <t xml:space="preserve">Mətn kimi göstərilir və ya dostane xəta</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-004: WAF xam xəta səhifəsi</t>
+    <t xml:space="preserve">BUG-027: WAF xam xəta səhifəsi</t>
   </si>
   <si>
     <t xml:space="preserve">UI-CRD-007</t>
@@ -2578,7 +2578,7 @@
     <t xml:space="preserve">Hər kartda "Kartın qiyməti" və "Müddət" var</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-008: Platinum və Maaş kartında qiymət yoxdur</t>
+    <t xml:space="preserve">BUG-029: Platinum və Maaş kartında qiymət yoxdur</t>
   </si>
   <si>
     <t xml:space="preserve">UI-CRD-012</t>
@@ -2593,7 +2593,7 @@
     <t xml:space="preserve">Slug-əsaslı ardıcıl ünvanlar</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-007: rəqəm və slug qarışıqdır</t>
+    <t xml:space="preserve">Müşahidə: rəqəm və slug qarışıqdır</t>
   </si>
   <si>
     <t xml:space="preserve">UI-CRD-013</t>
@@ -2695,7 +2695,7 @@
     <t xml:space="preserve">/az/kreditler/nagd-pul-krediti/133 açılır</t>
   </si>
   <si>
-    <t xml:space="preserve">Avtomatik; OBS-007</t>
+    <t xml:space="preserve">Avtomatik; Müşahidə</t>
   </si>
   <si>
     <t xml:space="preserve">UI-LON-014</t>
@@ -2710,7 +2710,7 @@
     <t xml:space="preserve">Hamısı /kartlar/kredit-kartlari altındadır</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-007: bir hissəsi /kreditler/kredit-kartlari-na aparır</t>
+    <t xml:space="preserve">Müşahidə: bir hissəsi /kreditler/kredit-kartlari-na aparır</t>
   </si>
   <si>
     <t xml:space="preserve">UI-DEP-007</t>
@@ -2881,7 +2881,7 @@
     <t xml:space="preserve">Xəta mesajı və ya minimum dəyər</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-013: nəticə sahələri yox olur</t>
+    <t xml:space="preserve">137 ay üçün "hesablama mövcud deyil" mesajı göstərilir</t>
   </si>
   <si>
     <t xml:space="preserve">UI-DEP-018</t>
@@ -2950,7 +2950,7 @@
     <t xml:space="preserve">Eyni tətbiq linki</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-006</t>
+    <t xml:space="preserve">Footer və DostBank linkləri uyğundur</t>
   </si>
   <si>
     <t xml:space="preserve">UI-ONL-007</t>
@@ -3106,7 +3106,7 @@
     <t xml:space="preserve">200 qaytarır</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-011: bəziləri yönləndirilir</t>
+    <t xml:space="preserve">BUG-030: bəziləri yönləndirilir</t>
   </si>
   <si>
     <t xml:space="preserve">UI-ABT-006</t>
@@ -3190,7 +3190,7 @@
     <t xml:space="preserve">script-src və digər direktivlər</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-010: yalnız upgrade-insecure-requests və frame-ancestors</t>
+    <t xml:space="preserve">Müşahidə: yalnız upgrade-insecure-requests və frame-ancestors</t>
   </si>
   <si>
     <t xml:space="preserve">UI-SEC-010</t>
@@ -3349,7 +3349,7 @@
     <t xml:space="preserve">Etibarlı XML, ünvanlar mövcuddur</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-011</t>
+    <t xml:space="preserve">BUG-030</t>
   </si>
   <si>
     <t xml:space="preserve">UI-PRF-011</t>
@@ -3376,7 +3376,7 @@
     <t xml:space="preserve">Çat düyməsi görünür</t>
   </si>
   <si>
-    <t xml:space="preserve">Real Chrome-da yoxlandı: çat düyməsi görünür (OBS-012 rədd edildi)</t>
+    <t xml:space="preserve">Real Chrome-da yoxlandı: çat düyməsi görünür</t>
   </si>
   <si>
     <t xml:space="preserve">UI-BRN-008</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">Yazılan rəqəm sahədə qalır (100 üstünə əlavə olunmur)</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-014 (Selenium diaqnostikası)</t>
+    <t xml:space="preserve">Əl ilə təkrarlanmır (Selenium artefaktı)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-DEP-020</t>
@@ -4013,6 +4013,48 @@
   </si>
   <si>
     <t xml:space="preserve">İcradan sonra yenilənir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nağd GBP və RUB məzənnə fərqi (spred) geniş: GBP 2.0000/2.2800, RUB 1.2000/2.0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bug yox, bank qərarı ola bilər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konvertor xarici valyutadan AZN-ə çevirmədə Satış məzənnəsini istifadə edir (100 USD → 170.00 AZN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maliyyə məlumatıdır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biznesdən təsdiq almaq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kart və kredit detal ünvanları ardıcıl deyil (rəqəm və slug qarışıqdır, /kartlar və /kreditler)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funksional problem yoxdur; SEO və saxlanılabilirlik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ünvan qaydasını standartlaşdırmaq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İlk açılışda izləmə kukiləri razılıq soruşulmadan qurulur (_ga, _fbp, _ym_uid və s.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qanunvericiliyə uyğunluq riski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hüquq şöbəsi qiymətləndirməlidir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSP başlığı məhduddur, Permissions-Policy yoxdur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Təhlükəsizlik möhkəmləndirməsi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Təhlükəsizlik komandasına ötürmək</t>
   </si>
 </sst>
 </file>
@@ -16683,7 +16725,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -16829,6 +16871,91 @@
         <v>1311</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1325</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E8"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/Final_Project_UI_Test_Cases.xlsx
+++ b/docs/Final_Project_UI_Test_Cases.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Uğursuz</t>
   </si>
   <si>
-    <t xml:space="preserve">/en məzmunu İngilis dilindədir, lakin html lang="az" və başlıq Azərbaycan dilində qalır (BUG-032)</t>
+    <t xml:space="preserve">/en məzmunu İngilis dilindədir, lakin html lang="az" və başlıq Azərbaycan dilində qalır (BUG-008, BUG-009)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-LNG-004</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Məzmun Rus dilindədir; html lang="ru"</t>
   </si>
   <si>
-    <t xml:space="preserve">/ru məzmunu Rus dilindədir, lakin html lang="az" və başlıq Azərbaycan dilində qalır (BUG-032)</t>
+    <t xml:space="preserve">/ru məzmunu Rus dilindədir, lakin html lang="az" və başlıq Azərbaycan dilində qalır (BUG-008, BUG-009)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-LNG-005</t>

--- a/docs/Final_Project_UI_Test_Cases.xlsx
+++ b/docs/Final_Project_UI_Test_Cases.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3607" uniqueCount="1332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3627" uniqueCount="1344">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -1450,7 +1450,7 @@
     <t xml:space="preserve">Bitmiş kampaniya aktiv kimi görünmür</t>
   </si>
   <si>
-    <t xml:space="preserve">Vaxtı bitmiş müsabiqə (17–27 iyul 2026) hələ də siyahıdadır (BUG-031)</t>
+    <t xml:space="preserve">Vaxtı bitmiş müsabiqə (17–27 iyul 2026) hələ də siyahıdadır (Müşahidə)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-CMP-003</t>
@@ -1495,7 +1495,7 @@
     <t xml:space="preserve">Məlumat və keçidlər düzgündür</t>
   </si>
   <si>
-    <t xml:space="preserve">/az/biznes: biznes kreditləri bannerləri və Müraciət et düymələri var; başlıq ana səhifə başlığıdır (BUG-032-a baxın)</t>
+    <t xml:space="preserve">/az/biznes: biznes kreditləri bannerləri və Müraciət et düymələri var; başlıq ana səhifə başlığıdır (Müşahidə-a baxın)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-ABT-001</t>
@@ -2053,7 +2053,7 @@
     <t xml:space="preserve">Mətn kimi göstərilir</t>
   </si>
   <si>
-    <t xml:space="preserve">WAF "&lt;" simvolunu bloklayır (BUG-027)</t>
+    <t xml:space="preserve">WAF "&lt;" simvolunu bloklayır (Müşahidə)</t>
   </si>
   <si>
     <t xml:space="preserve">UI-SEC-005</t>
@@ -2505,7 +2505,7 @@
     <t xml:space="preserve">"Nəticə tapılmadı" mesajı</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-028: yalnız "0 Nəticə"</t>
+    <t xml:space="preserve">Müşahidə: yalnız "0 Nəticə"</t>
   </si>
   <si>
     <t xml:space="preserve">UI-SRC-009</t>
@@ -2523,7 +2523,7 @@
     <t xml:space="preserve">Mətn kimi göstərilir və ya dostane xəta</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-027: WAF xam xəta səhifəsi</t>
+    <t xml:space="preserve">Müşahidə: WAF xam xəta səhifəsi</t>
   </si>
   <si>
     <t xml:space="preserve">UI-CRD-007</t>
@@ -2596,7 +2596,7 @@
     <t xml:space="preserve">Hər kartda "Kartın qiyməti" və "Müddət" var</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-029: Platinum və Maaş kartında qiymət yoxdur</t>
+    <t xml:space="preserve">Müşahidə: Platinum və Maaş kartında qiymət yoxdur</t>
   </si>
   <si>
     <t xml:space="preserve">UI-CRD-012</t>
@@ -4073,6 +4073,42 @@
   </si>
   <si>
     <t xml:space="preserve">Təhlükəsizlik komandasına ötürmək</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axtarışda "&lt;" simvolu olan sorğu WAF-ın xam xəta səhifəsini göstərir (XSS bloklanır, amma istifadəçi təcrübəsi pisdir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İstifadəçiyə dostane mesaj göstərmək</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nəticəsiz axtarışda "tapılmadı" mesajı yoxdur, yalnız "0 Nəticə" göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesaj əlavə etmək</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debet kart siyahısında Platinum və Maaş kartında qiymət göstərilmir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Məzmun uyğunsuzluğu ola bilər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaxtı bitmiş müsabiqə (17–27 iyul 2026) hələ də kampaniyalar siyahısındadır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitmiş kampaniyaları gizlətmək</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daxili səhifələrdə canonical linki həmişə /az ana səhifəsinə işarə edir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical-ı səhifənin öz ünvanına yönəltmək</t>
   </si>
 </sst>
 </file>
@@ -16755,7 +16791,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -16986,6 +17022,91 @@
         <v>1331</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1343</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E8"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
